--- a/data/capstone-stratified-customer-survey.xlsx
+++ b/data/capstone-stratified-customer-survey.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -16791,7 +16791,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -17190,7 +17190,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -17248,7 +17248,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -18319,7 +18319,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18423,7 +18423,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -18469,7 +18469,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -18567,7 +18567,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -18654,7 +18654,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -19116,7 +19116,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -19353,7 +19353,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -20151,7 +20151,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -20180,7 +20180,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -20475,7 +20475,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -20579,7 +20579,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -20712,7 +20712,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -20822,7 +20822,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -20909,7 +20909,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -21071,7 +21071,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -21100,7 +21100,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -21146,7 +21146,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -21169,7 +21169,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -21314,7 +21314,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -21343,7 +21343,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -21366,7 +21366,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -21441,7 +21441,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -21551,7 +21551,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -21927,7 +21927,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -22014,7 +22014,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -22257,7 +22257,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -22425,7 +22425,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -22593,7 +22593,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -22651,7 +22651,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -22726,7 +22726,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -22847,7 +22847,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -22980,7 +22980,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -23055,7 +23055,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -23188,7 +23188,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -23292,7 +23292,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -23437,7 +23437,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -23593,7 +23593,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -23743,7 +23743,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -23772,7 +23772,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -23801,7 +23801,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -23830,7 +23830,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -23969,7 +23969,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -24021,7 +24021,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -24050,7 +24050,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -24108,7 +24108,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -24363,7 +24363,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -24571,7 +24571,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -24669,7 +24669,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -24744,7 +24744,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -24819,7 +24819,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -24981,7 +24981,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -25056,7 +25056,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -25102,7 +25102,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -25125,7 +25125,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -25148,7 +25148,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -25177,7 +25177,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -25223,7 +25223,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -25246,7 +25246,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -25275,7 +25275,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -25356,7 +25356,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -25489,7 +25489,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -25512,7 +25512,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -25622,7 +25622,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -25645,7 +25645,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -25784,7 +25784,7 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -25813,7 +25813,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -25888,7 +25888,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -26154,7 +26154,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -26183,7 +26183,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
@@ -26229,7 +26229,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -26298,7 +26298,7 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -26344,7 +26344,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
@@ -26367,7 +26367,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -26425,7 +26425,7 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
@@ -26512,7 +26512,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -26720,7 +26720,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -26743,7 +26743,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
@@ -26772,7 +26772,7 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -26882,7 +26882,7 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -26911,7 +26911,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -26940,7 +26940,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
@@ -26998,7 +26998,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -27067,7 +27067,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -27096,7 +27096,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -27119,7 +27119,7 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -27171,7 +27171,7 @@
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
@@ -27223,7 +27223,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -27252,7 +27252,7 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
@@ -27310,7 +27310,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -27333,7 +27333,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
@@ -27362,7 +27362,7 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -27692,7 +27692,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -27721,7 +27721,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -27750,7 +27750,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
@@ -27773,7 +27773,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
@@ -27831,7 +27831,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -28051,7 +28051,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
@@ -28074,7 +28074,7 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -28155,7 +28155,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
@@ -28282,7 +28282,7 @@
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
@@ -28311,7 +28311,7 @@
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
@@ -28340,7 +28340,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
@@ -28398,7 +28398,7 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -28427,7 +28427,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
@@ -28450,7 +28450,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -28502,7 +28502,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -28641,7 +28641,7 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
@@ -28664,7 +28664,7 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -28722,7 +28722,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
@@ -28774,7 +28774,7 @@
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -28907,7 +28907,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -28936,7 +28936,7 @@
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -28959,7 +28959,7 @@
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
@@ -28988,7 +28988,7 @@
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -29046,7 +29046,7 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -29069,7 +29069,7 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -29098,7 +29098,7 @@
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
@@ -29144,7 +29144,7 @@
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
@@ -29289,7 +29289,7 @@
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -29393,7 +29393,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
@@ -29480,7 +29480,7 @@
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -29503,7 +29503,7 @@
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
@@ -29549,7 +29549,7 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
@@ -29578,7 +29578,7 @@
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
@@ -29636,7 +29636,7 @@
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -29665,7 +29665,7 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
@@ -29763,7 +29763,7 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
@@ -29792,7 +29792,7 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
@@ -29821,7 +29821,7 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
@@ -29844,7 +29844,7 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
@@ -29971,7 +29971,7 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
@@ -30023,7 +30023,7 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
@@ -30075,7 +30075,7 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
@@ -30104,7 +30104,7 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
@@ -30162,7 +30162,7 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -30191,7 +30191,7 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
@@ -30220,7 +30220,7 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -30243,7 +30243,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
@@ -30301,7 +30301,7 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1118" t="inlineStr">
@@ -30353,7 +30353,7 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
@@ -30457,7 +30457,7 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
@@ -30509,7 +30509,7 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
@@ -30590,7 +30590,7 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
@@ -30642,7 +30642,7 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
@@ -30671,7 +30671,7 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
@@ -30700,7 +30700,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
@@ -30810,7 +30810,7 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
@@ -30839,7 +30839,7 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
@@ -30885,7 +30885,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
@@ -30943,7 +30943,7 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
@@ -31001,7 +31001,7 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
@@ -31047,7 +31047,7 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
@@ -31070,7 +31070,7 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
@@ -31116,7 +31116,7 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
@@ -31145,7 +31145,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
@@ -31249,7 +31249,7 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
@@ -31272,7 +31272,7 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
@@ -31301,7 +31301,7 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
@@ -31353,7 +31353,7 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
@@ -31399,7 +31399,7 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
@@ -31538,7 +31538,7 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
@@ -31567,7 +31567,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
@@ -31596,7 +31596,7 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
@@ -31619,7 +31619,7 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
@@ -31671,7 +31671,7 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
@@ -31700,7 +31700,7 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
@@ -31723,7 +31723,7 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
@@ -31804,7 +31804,7 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
@@ -31827,7 +31827,7 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
@@ -31856,7 +31856,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
@@ -31995,7 +31995,7 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
@@ -32047,7 +32047,7 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
@@ -32134,7 +32134,7 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
@@ -32180,7 +32180,7 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
@@ -32209,7 +32209,7 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
@@ -32290,7 +32290,7 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
@@ -32348,7 +32348,7 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
@@ -32371,7 +32371,7 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
@@ -32423,7 +32423,7 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
@@ -32446,7 +32446,7 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
@@ -32469,7 +32469,7 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
@@ -32492,7 +32492,7 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C1201" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C1203" t="inlineStr">
@@ -32622,7 +32622,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -32644,7 +32644,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -32688,7 +32688,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -32746,7 +32746,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -32755,13 +32755,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3663</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -32770,13 +32770,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3261</v>
+        <v>5665</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -32785,13 +32785,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1076</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -32800,13 +32800,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3887</v>
+        <v>5389</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -32815,13 +32815,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5665</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -32830,13 +32830,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4448</v>
+        <v>5451</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -32845,13 +32845,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5389</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -32860,13 +32860,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7160</v>
+        <v>7571</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -32875,13 +32875,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5451</v>
+        <v>7608</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -32890,13 +32890,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4821</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -32905,13 +32905,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7571</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -32920,7 +32920,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7608</v>
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
@@ -32968,7 +32968,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -32984,7 +32984,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Midlands</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -33016,7 +33016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -33103,7 +33103,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>North / Midlands / South / London</t>
+          <t>Northeast / Midwest / South / West</t>
         </is>
       </c>
     </row>
@@ -33248,7 +33248,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   population, concentrated among younger customers and in London. That is COVERAGE ERROR and</t>
+          <t xml:space="preserve">   population, concentrated among younger customers and in the West. That is COVERAGE ERROR and</t>
         </is>
       </c>
     </row>
@@ -33311,7 +33311,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   using pilot standard deviations. London is deliberately over-sampled relative to its share</t>
+          <t xml:space="preserve">   using pilot standard deviations. The West is deliberately over-sampled relative to its share</t>
         </is>
       </c>
     </row>
